--- a/project-documents/summer-prep-background/ESABCC_Policy-Gaps_Transport-Industry_2026-07.xlsx
+++ b/project-documents/summer-prep-background/ESABCC_Policy-Gaps_Transport-Industry_2026-07.xlsx
@@ -460,9 +460,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Gap landscape'!$A$6:$A$9</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -488,9 +488,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Gap landscape'!$A$6:$A$9</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -516,9 +516,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Gap landscape'!$A$6:$A$9</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -544,9 +544,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Gap landscape'!$A$6:$A$9</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -564,6 +564,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -582,6 +583,7 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <spPr>
           <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:solidFill>
@@ -620,9 +622,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <spPr>
           <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:solidFill>
@@ -745,9 +749,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Gap landscape'!$A$15:$A$20</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -773,9 +777,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Gap landscape'!$A$15:$A$20</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -801,9 +805,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Gap landscape'!$A$15:$A$20</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -829,9 +833,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Gap landscape'!$A$15:$A$20</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -849,6 +853,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -867,6 +872,7 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <spPr>
           <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:solidFill>
@@ -905,9 +911,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <spPr>
           <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:solidFill>

--- a/project-documents/summer-prep-background/ESABCC_Policy-Gaps_Transport-Industry_2026-07.xlsx
+++ b/project-documents/summer-prep-background/ESABCC_Policy-Gaps_Transport-Industry_2026-07.xlsx
@@ -1727,7 +1727,7 @@
       </c>
       <c r="K2" s="15" t="inlineStr">
         <is>
-          <t>The Ecodesign for Sustainable Products Regulation (ESPR, 2024) and the CEAP-2 workstream push design, durability and reuse upstream of recycling for the first time — but the prevention/waste-hierarchy tilt is still early and product-group delegated acts are pending, so the gap is narrowed, not closed.</t>
+          <t>The Ecodesign for Sustainable Products Regulation (ESPR, Reg. (EU) 2024/1781) operationalises the design, durability and reuse agenda that CEAP 2 (COM(2020) 98 final, 11 March 2020) had already set out — so this is the delivery of an existing direction, not a first move. The gap stays open at both ends: the successor Circular Economy Act has not been tabled (expected Q3–Q4 2026), and although the ESPR working plan was adopted on 16 April 2025 (2025–2030, six priority groups, iron &amp; steel first with an indicative 2026 delegated act), no product-group delegated act has been adopted as of July 2026.</t>
         </is>
       </c>
       <c r="L2" s="15" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
-          <t>The Ecodesign Directive has been mainly focused on energy efficiency; product circularity has been added only in recent years, and its scope remained limited to energy products.</t>
+          <t>The Ecodesign Directive has been mainly focused on energy efficiency; product circularity has been added in recent years, and its scope remained limited to energy products.</t>
         </is>
       </c>
       <c r="G3" s="23" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="K3" s="23" t="inlineStr">
         <is>
-          <t>Largely closed: the ESPR (Reg. (EU) 2024/1781) replaces the old energy-only Ecodesign Directive and extends the framework to almost all physical product groups. Effect now depends on the pace of delegated acts (implementation risk remains).</t>
+          <t>Largely closed: the ESPR (Reg. (EU) 2024/1781 of 13 June 2024, in force 18 July 2024) replaces the old energy-only Ecodesign Directive 2009/125/EC and extends the framework to physical products generally — subject to the Art. 1(2) carve-outs for food, feed, medicinal products, living plants, animals and micro-organisms, products of human origin and vehicles under Reg. (EU) 2018/858. Effect now depends on the pace of delegated acts, and none has yet been adopted for a product group (implementation risk remains).</t>
         </is>
       </c>
       <c r="L3" s="23" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="K4" s="15" t="inlineStr">
         <is>
-          <t>The Net-Zero Industry Act (2024) and the 2025 Clean Industrial Deal add lead-market and demand-side tools (e.g. non-price criteria in public procurement and auctions, planned resilience/green-content requirements). Coverage of early deployment / market formation is improving but still thin versus the R&amp;D and diffusion ends.</t>
+          <t>The Net-Zero Industry Act (Reg. (EU) 2024/1735) and the 2025 Clean Industrial Deal add lead-market and demand-side tools: NZIA Arts 25 and 26 bring non-price criteria into public procurement and renewables auctions, with the implementing act obliging Member States to apply them from 30 December 2025 to at least 30 % of annually auctioned capacity or at least 6 GW, and Commission guidance on Arts 25–26 followed on 22 July 2026. The Industrial Accelerator Act proposed on 4 March 2026 adds binding low-carbon procurement content on top. Coverage of early deployment / market formation is improving but still thin versus the R&amp;D and diffusion ends.</t>
         </is>
       </c>
       <c r="L4" s="15" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="K5" s="23" t="inlineStr">
         <is>
-          <t>CO₂ standards for cars and vans still reward zero-tailpipe rather than vehicle efficiency; the 2025/2026 review of the standards is the moment to close it, but nothing is adopted. Assessed unchanged.</t>
+          <t>CO₂ standards for cars and vans still reward zero-tailpipe rather than vehicle efficiency. The review has since been delivered — COM(2025) 995 of 16 December 2025, in the Automotive Package — and it contains the first size/efficiency lever inside the ZEV segment: super-credits for a new 'small affordable electric car' class (≤4.2 m, with mass, width, wheel-size and motor-power criteria). The same proposal would cut the 2035 target from 100 % to 90 % and the 2030 van target from 50 % to 40 %. Nothing is adopted: Council was divided in March 2026 and the EP rapporteur's draft report came in April 2026. Status open, but the file to watch is now identified.</t>
         </is>
       </c>
       <c r="L5" s="23" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
-          <t>The TEN-T recast (Reg. (EU) 2024/1679) is in force and addresses some ambition weaknesses, but the Combined Transport Directive recast came close to being withdrawn by the Commission in late 2025, was kept alive only after Parliament rejected the withdrawal (Jan 2026), and remains stalled in Council with no agreed text as of mid-2026 — the ambition gap is unresolved and the file’s survival itself is in question.</t>
+          <t>The TEN-T recast (Reg. (EU) 2024/1679) has applied since 18 July 2024 and answers the report's specific finding on terminal capacity: Art. 36(4) requires Member States to complete an analysis of multimodal freight terminals and adopt action plans by 19 July 2028, feeding corridor work plans due 19 July 2026. Regulation (EU) 2026/1184 of 20 May 2026 on railway infrastructure capacity then replaces the delivery architecture the report criticised, repealing the Rail Freight Corridors Regulation (EU) No 913/2010 with effect from 14 December 2030. Against that, the Combined Transport Directive recast is in limbo: the Commission announced its INTENTION to withdraw COM(2023) 702 in its 2026 Work Programme (adopted 21 October 2025) — the proposal has never been formally withdrawn and the file still reads 'awaiting committee decision' — a majority of political groups rejected the withdrawal at the end of January 2026 (exact date and forum unverified), and the June 2026 TTE Council reached no general approach. The ambition gap is narrowed on terminals and rail capacity but unresolved on combined transport.</t>
         </is>
       </c>
       <c r="L6" s="15" t="inlineStr">
@@ -2018,7 +2018,7 @@
       <c r="M6" s="20" t="inlineStr">
         <is>
           <t>https://www.railwaygazette.com/freight/2026/06/04/rail-association-throw-last-hail-mary-to-save-combined-transport-directive/
-https://www.cer.be/cer-press-releases/council-faces-stalemate-as-combined-transport-directive-loses-momentum</t>
+https://oeil.europarl.europa.eu/oeil/en/procedure-file?reference=2023/0396(COD)</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>Implementation of the modal-shift measures (notably the Rail Freight Corridor Regulation and the Combined Transport Directive) has been incomplete and heterogeneous across Member States.</t>
+          <t>Implementation of the modal-shift measures has been incomplete and heterogeneous across Member States.</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="K7" s="23" t="inlineStr">
         <is>
-          <t>Implementation across Member States remains heterogeneous; the new TEN-T deadlines are not yet in force. Assessed unchanged.</t>
+          <t>Implementation across Member States remains heterogeneous. The TEN-T Regulation itself has applied since 18 July 2024 — it is its milestones that have not yet fallen due (terminal analysis 19 July 2028; network completion 2030/2040/2050) — and Reg. (EU) 2026/1184 only bites from December 2030, so implementation is still largely untested. Assessed unchanged.</t>
         </is>
       </c>
       <c r="L7" s="23" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>Extra-EU aviation still sits under CORSIA rather than the ETS, and half of extra-EU maritime remains outside the ETS; the review clauses have not changed the scope. Assessed unchanged (also applies to Maritime).</t>
+          <t>Extra-EU aviation still sits under CORSIA rather than the ETS, and half of extra-EU maritime remains outside it — but the review clause has now been acted on. On 17 July 2026 the Commission adopted COM(2026) 616 final (2026/0212(COD)), finding under Art. 28b(3) that CORSIA-participating states cover less than 70 % of international aviation emissions, and proposing to extend the ETS from 1 January 2029 to 31 December 2032 to flights departing the EEA for aerodromes within 5 000 km of Frankfurt, subject to a 2032 review. Long-haul (US, Brazil, India, China, Far East) would stay exempt and nothing is adopted, so the gap remains open — but it is no longer true that the review clauses have not changed the scope. The maritime half is unchanged: the proposal reproduces Art. 3ga(1) with the 50 % extra-EU voyage share intact.</t>
         </is>
       </c>
       <c r="L8" s="15" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>There are well-founded suspicions of fraud in the labelling of transport biofuels as sustainable under RED III.</t>
+          <t>There are well-founded suspicions of fraud in the labelling of transport biofuels as sustainable.</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="K11" s="23" t="inlineStr">
         <is>
-          <t>The Union Database for Biofuels has been operational since January 2024 and stricter voluntary-scheme oversight tightens traceability, but the delegated act setting a binding mandatory-use/sanctions date is still pending agreement with Member States as of 2025–2026 — enforcement teeth are not yet in place, so the implementation gap is narrowed, not resolved.</t>
+          <t>The Union Database for Biofuels has been operational since 15 January 2024 (gaseous fuels added end-November 2024), but the delegated act setting a binding mandatory-use/sanctions date is still a tabled draft as of July 2026 — it slipped past its end-2025 target and the mandatory-use date was the last open item. The revision of Implementing Regulation (EU) 2022/996 on voluntary schemes, often cited as the tightening step, is not expected before end-2026. Enforcement teeth are not yet in place, so the implementation gap is narrowed, not resolved.</t>
         </is>
       </c>
       <c r="L11" s="23" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="M11" s="28" t="inlineStr">
         <is>
-          <t>https://vespertool.com/blog/the-udb-will-be-mandatory/
+          <t>https://energy.ec.europa.eu/topics/renewable-energy/bioenergy/biofuels/union-database-liquid-and-gaseous-renewable-and-recycled-carbon-fuels_en
 https://energy.ec.europa.eu/news/eu-database-biofuels-becomes-operational-2024-01-15_en</t>
         </is>
       </c>
@@ -2518,13 +2518,13 @@
       </c>
       <c r="H2" s="15" t="inlineStr">
         <is>
-          <t>A draft Industrial Accelerator Act (renamed from "Industrial Decarbonisation Accelerator Act" in von der Leyen’s Sept-2025 State of the Union address) was tabled 4 March 2026 with "Made in EU" / low-carbon procurement content among its core measures — the gap is now "policy proposed, not yet enacted", not a purely hypothetical future test. Confirmed if the Act is adopted without binding near-zero-steel content/procurement quotas, or stalls before adoption; refuted if the adopted Act sets enforceable near-zero-steel demand.</t>
+          <t>A draft Industrial Accelerator Act (renamed from "Industrial Decarbonisation Accelerator Act" — the earlier title is used in the Steel and Metals Action Plan of 19 March 2025, and the SOTEU 2025 Letter of Intent of 10 September 2025 lists it under the new name) was tabled 4 March 2026 with "Made in EU" / low-carbon procurement content among its core measures — the gap is now "policy proposed, not yet enacted", not a purely hypothetical future test. The tabled text (COM(2026) 100 final, 2026/0068(COD)) already sets binding thresholds — at least 25 % low-carbon steel, 25 % low-carbon and Union-origin aluminium, and at least 5 % low-carbon and Union-origin concrete/mortar in publicly supported construction, pegged to standards to be set by CPR and ESPR delegated acts — but it nowhere uses 'near-zero' and sets no near-zero quota. So the candidate now reads: binding LOW-CARBON procurement proposed, NEAR-ZERO still unaddressed. Confirmed if the Act is adopted with low-carbon thresholds only, or stalls; refuted if the adopted Act sets enforceable near-zero-steel demand. In first reading (joint INTA/ITRE/IMCO, rapporteurs appointed 29 April 2026, indicative plenary 14 December 2026).</t>
         </is>
       </c>
       <c r="I2" s="20" t="inlineStr">
         <is>
           <t>https://www.sidley.com/en/insights/newsupdates/2026/04/industrial-accelerator-act
-https://single-market-economy.ec.europa.eu/publications/industrial-accelerator-act_en</t>
+https://oeil.europarl.europa.eu/oeil/en/procedure-file?reference=2026/0068(COD)</t>
         </is>
       </c>
       <c r="J2" s="33" t="inlineStr"/>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="H3" s="23" t="inlineStr">
         <is>
-          <t>Confirmed if operational/committed storage &amp; transport capacity stays below the trajectory needed for cement process emissions; refuted if storage FIDs and CO₂ networks scale to meet the 50 Mt/yr target on time.</t>
+          <t>Confirmed if operational/committed storage &amp; transport capacity stays below the trajectory needed for cement process emissions; refuted if storage FIDs and CO₂ networks scale to meet the 50 Mt/yr target on time. UPDATE (July 2026): obligated entities are on track for roughly 29 Mt and Member State plans for roughly 33 Mt against the 50 Mt NZIA Art. 23 target, with Porthos, Greensand and Prinos operational or near-operational and seven further sites totalling about 19 Mt. The CO2 transport and market package slipped from 2025 and is expected within the Energy Union package in Q3 2026, so there is still no tabled EU proposal on CO2 transport infrastructure — the strongest support for this candidate.</t>
         </is>
       </c>
       <c r="I3" s="28" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="H4" s="15" t="inlineStr">
         <is>
-          <t>Confirmed if no instrument sets a feedstock-defossilisation signal or CCU/recycled-carbon accounting rule; refuted if such a framework is proposed.</t>
+          <t>Confirmed if no instrument sets a feedstock-defossilisation signal or CCU/recycled-carbon accounting rule; refuted if such a framework is proposed. UPDATE (July 2026): as written this test is already partly tripped. Commission Implementing Decision (EU) 2026/1425 of 30 June 2026 lays down mass-balance rules for recycled plastic content in single-use plastic beverage bottles, and the Chemicals Industry Action Plan of 8 July 2025 commits to incentivising clean carbon sources. Narrow the refutation condition to a binding, SECTOR-WIDE feedstock-defossilisation signal; these two are partial and sector-limited. Whether the July-2026 ETS review extends surrender-obligation exemptions to carbon embedded in products is unverified.</t>
         </is>
       </c>
       <c r="I4" s="20" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t>Confirmed if connection lead-times and industrial power prices remain binding constraints without a targeted instrument; refuted if the Affordable Energy / grid package resolves them.</t>
+          <t>Confirmed if connection lead-times and industrial power prices remain binding constraints without a targeted instrument; refuted if the Affordable Energy / grid package resolves them. UPDATE (July 2026): the premise that grid access and power prices are not treated as a decarbonisation barrier in their own right no longer holds — the European Grids Package (10 December 2025) carries guidance on preventing and clearing connection queues plus eight prioritised energy highways, and the Electrification Action Plan (17 July 2026) targets the electricity-versus-fossil price gap directly, enabling Member States to cut network charges for certain consumer groups and taxes for energy-intensive businesses, against a 23%-to-46%-by-2040 electrification pathway and the Clean Industrial Deal 32%-by-2030 KPI. Read this as a DELIVERY gap and test it in outcome terms — connection lead times actually falling, the industrial price gap actually narrowing — not on whether an instrument exists.</t>
         </is>
       </c>
       <c r="I5" s="28" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>Confirmed if support instruments carry no water-stress conditionality; refuted if a water screen is added to siting/funding criteria.</t>
+          <t>Confirmed if support instruments carry no water-stress conditionality; refuted if a water screen is added to siting/funding criteria. UPDATE (July 2026): the European Water Resilience Strategy of 4 June 2025 names hydrogen, batteries, CCS, semiconductors and data centres as water-intensive strategic technologies and calls for water to be integrated into EU industrial policy — a non-binding counterweight, not a siting or funding condition. The absence of a water criterion in NZIA, Hydrogen Bank auction terms and State-aid/IPCEI rules is evidence of absence from the documents checked, not a confirmed absence in the legal texts.</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>Confirmed if no EU instrument steers company-car/road-pricing reform; refuted if the ETD recast or a pricing framework does.</t>
+          <t>Confirmed if no EU instrument steers company-car/road-pricing reform; refuted if the ETD recast or a pricing framework does. UPDATE (July 2026): narrow this to FISCAL levers. The Clean Corporate Vehicles Regulation proposed on 16 December 2025 would oblige Member States to ensure minimum zero- and low-emission shares of new corporate car and van registrations by large undertakings from 2030 — corporate vehicles are around 60% of new cars and up to 90% of new vans — but it regulates registrations, not taxation. The Eurovignette targeted revision (proposal 2 October 2025, Council mandate 4 March 2026, provisional agreement 30 June 2026) is heavy-duty only. Company-car tax treatment and distance- or CO2-based charging for light vehicles remain unaddressed.</t>
         </is>
       </c>
       <c r="I7" s="28" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>Confirmed if MCS/H₂ corridor coverage stays below the truck-fleet trajectory; refuted if AFIR delivery keeps pace.</t>
+          <t>Confirmed if MCS/H₂ corridor coverage stays below the truck-fleet trajectory; refuted if AFIR delivery keeps pace. CONFIRMED (July 2026): the 2024 HDV CO2 standards are Regulation (EU) 2024/1610 of 14 May 2024 (-45% from 2030, -65% from 2035, -90% from 2040; 100% zero-emission urban buses by 2035), and the AFIR review proposal is expected in Q4 2026 — the natural checkpoint for this test.</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>Confirmed if electrification funding carries no binding adaptation/climate-proofing condition; refuted if TEN-T climate-proofing is enforced on rail works.</t>
+          <t>Confirmed if electrification funding carries no binding adaptation/climate-proofing condition; refuted if TEN-T climate-proofing is enforced on rail works. UPDATE (July 2026): the premise is largely refuted as worded. Regulation (EU) 2024/1679 requires climate resilience to be taken into account when projects of common interest are planned, and makes projects requiring an EIA under Directive 2011/92/EU subject to climate proofing per Commission Notice 2021/C 373/01; corridor work plans must analyse climate-change impacts. Reframe as an IMPLEMENTATION gap — no adaptation performance standards, no coverage of sub-EIA or nationally funded electrification works, no monitoring of whether climate proofing is applied. The final article number should be checked against the OJ before use.</t>
         </is>
       </c>
       <c r="I9" s="28" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>Confirmed if non-CO₂ effects remain only monitored, not acted on, after the MRV review; refuted if a mitigation/pricing measure is introduced.</t>
+          <t>Confirmed if non-CO₂ effects remain only monitored, not acted on, after the MRV review; refuted if a mitigation/pricing measure is introduced. UPDATE (July 2026): "only an MRV step exists" is no longer accurate at proposal level. COM(2026) 616 of 17 July 2026 proposes an amended Art. 3c(6) reserving up to 3 million allowances until 31 December 2033 for cost-effective contrail mitigation, allocating allowances worth 0.1% of verified emissions to operators that embed contrail forecasting in flight planning. Read the test as refuted only if a mitigation or pricing measure is ADOPTED; the Art. 14(5) MRV review report is due 31 December 2027.</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>Confirmed if RFNBO uptake stays below 1% of maritime fuel use through 2031 (triggering the conditional 2034 sub-target) and/or OPS installation at major EU ports continues to lag the 1 January 2030 AFIR deadline; refuted if RFNBO/biofuel supply and port electrification scale to meet the FuelEU trajectory on schedule.</t>
+          <t>Confirmed if RFNBO uptake stays below 1% of maritime fuel use through 2031 (triggering the conditional 2034 sub-target) and/or OPS installation at major EU ports continues to lag the 1 January 2030 AFIR deadline; refuted if RFNBO/biofuel supply and port electrification scale to meet the FuelEU trajectory on schedule. CORRECTION (July 2026): the "~20% contracted or installed by May 2025" figure is not in the cited source. The source says 51 ports across 15 coastal Member States offered shore power with 309 MW installed as of May 2025, against a need to triple or quadruple capacity by 2030. COM(2026) 616 of 17 July 2026 also proposes a Sustainable Maritime Alternative Propulsion mechanism (new Art. 3gaa) recycling ETS revenue into sustainable maritime fuels — a partial response on the supply condition.</t>
         </is>
       </c>
       <c r="I11" s="28" t="inlineStr">

--- a/project-documents/summer-prep-background/ESABCC_Policy-Gaps_Transport-Industry_2026-07.xlsx
+++ b/project-documents/summer-prep-background/ESABCC_Policy-Gaps_Transport-Industry_2026-07.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Re-assessed gaps" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate gaps" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Landscape data" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap landscape" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Re-assessed gaps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Candidate gaps" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Landscape data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Gap landscape" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Legend" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Re-assessed gaps'!$A$1:$N$11</definedName>
@@ -410,13 +410,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1100" b="0">
                 <a:solidFill>
@@ -451,10 +451,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="B04545"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -479,10 +479,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="F59E2D"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -507,10 +507,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4D7E83"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -535,10 +535,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="B487C7"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -569,8 +569,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -585,7 +585,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="B9CFD1"/>
             </a:solidFill>
@@ -593,8 +593,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800">
                 <a:solidFill>
@@ -628,7 +628,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="B9CFD1"/>
             </a:solidFill>
@@ -636,8 +636,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800">
                 <a:solidFill>
@@ -664,8 +664,8 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="800">
               <a:solidFill>
@@ -690,7 +690,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -699,13 +699,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1100" b="0">
                 <a:solidFill>
@@ -740,10 +740,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="B04545"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -768,10 +768,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="F59E2D"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -796,10 +796,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4D7E83"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -824,10 +824,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="B487C7"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -858,8 +858,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -874,7 +874,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="B9CFD1"/>
             </a:solidFill>
@@ -882,8 +882,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800">
                 <a:solidFill>
@@ -917,7 +917,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="B9CFD1"/>
             </a:solidFill>
@@ -925,8 +925,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800">
                 <a:solidFill>
@@ -953,8 +953,8 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="800">
               <a:solidFill>
@@ -979,7 +979,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -988,7 +988,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -1003,9 +1003,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1025,9 +1025,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/project-documents/summer-prep-background/ESABCC_Policy-Gaps_Transport-Industry_2026-07.xlsx
+++ b/project-documents/summer-prep-background/ESABCC_Policy-Gaps_Transport-Industry_2026-07.xlsx
@@ -437,6 +437,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -580,6 +581,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -726,6 +728,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -869,6 +872,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -1015,7 +1019,7 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2664000"/>
